--- a/data/tableau_matieres_coefficients.xlsx
+++ b/data/tableau_matieres_coefficients.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bureau\GItHubUpload\rep_DECC\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LK\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4F270A-ED84-4155-9AAE-4AFDBCBAE1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A6B572-F360-45FC-BBBC-36F17D13688E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BEPC" sheetId="1" r:id="rId1"/>
@@ -2310,7 +2310,7 @@
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">

--- a/data/tableau_matieres_coefficients.xlsx
+++ b/data/tableau_matieres_coefficients.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LK\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bureau\GItHubUpload\Last_-DECC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A6B572-F360-45FC-BBBC-36F17D13688E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85771557-4620-4FB9-AEEC-BECADE7FFB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="176">
   <si>
     <t>Examen</t>
   </si>
@@ -563,6 +563,9 @@
   </si>
   <si>
     <t>INITIATION TO ECONOMICS</t>
+  </si>
+  <si>
+    <t>PHYSIQUE-CHIMIE-TECHNOLOGIE/ GREC</t>
   </si>
 </sst>
 </file>
@@ -1070,7 +1073,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>175</v>
       </c>
       <c r="C13">
         <v>2</v>

--- a/data/tableau_matieres_coefficients.xlsx
+++ b/data/tableau_matieres_coefficients.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bureau\GItHubUpload\Last_-DECC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85771557-4620-4FB9-AEEC-BECADE7FFB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771EF1B2-229F-435E-B6D5-C7560B4680E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BEPC" sheetId="1" r:id="rId1"/>
@@ -1076,7 +1076,7 @@
         <v>175</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1212,7 +1212,7 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">

--- a/data/tableau_matieres_coefficients.xlsx
+++ b/data/tableau_matieres_coefficients.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bureau\GItHubUpload\Last_-DECC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771EF1B2-229F-435E-B6D5-C7560B4680E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3AEC5A4-18F2-4AE5-9884-F07B1CDEAFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="175">
   <si>
     <t>Examen</t>
   </si>
@@ -563,16 +563,13 @@
   </si>
   <si>
     <t>INITIATION TO ECONOMICS</t>
-  </si>
-  <si>
-    <t>PHYSIQUE-CHIMIE-TECHNOLOGIE/ GREC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -584,6 +581,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2A37"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -621,11 +624,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1073,10 +1077,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>175</v>
+        <v>15</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1097,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -1105,7 +1109,7 @@
     <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1116,7 +1120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1127,7 +1131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1138,7 +1142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1149,7 +1153,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1160,7 +1164,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1171,7 +1175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -1182,7 +1186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1193,7 +1197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1203,8 +1207,9 @@
       <c r="C9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1212,10 +1217,10 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1226,7 +1231,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -1237,7 +1242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1248,7 +1253,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
